--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-04_leave_balances_休暇残日数_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-04_leave_balances_休暇残日数_テーブル詳細設計書.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち leave_balances を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.2 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -712,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F35"/>
+  <dimension ref="A2:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -735,15 +735,15 @@
       <c r="E2" s="9" t="n"/>
       <c r="F2" s="10" t="n"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="92" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>バックアップ</t>
+          <t>開発用の初期付与（DevLeaveBalanceInitializer）</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>BAT-003 の dump に含まれる。</t>
+          <t>開発環境のみ。kintaiflow.dev.seed-password が設定済みで、leave_balances が 0 件かつ users が 1 件以上のときだけ、起動時に ACTIVE の全ユーザーへ年次有給休暇 20.0 日（used_days=0）を 1 行ずつ作る。granted_on は起動日が属する年度の 4/1（4 月以降なら当年 4/1、1〜3 月なら前年 4/1）、expires_on は付与の 2 年後（LeaveBalanceService#grant）。毎年度 4/1 に自動で付与し直す仕組みではない（年度ごとの自動付与は BAT-001 の設計で、現行コードには未実装）。本番では seed-password を設定しないため動かない。付与日数は付与日数表（10〜20 日）とは無関係な開発用の固定値。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -751,15 +751,15 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="10" t="n"/>
     </row>
-    <row r="4" ht="63" customHeight="1">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>将来のパーティション/アーカイブ</t>
+          <t>バックアップ</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>当面不要（年 1,000 件）。5 年を超えた失効済み行は別表へ退避（管理簿の保存期間を満たす範囲で）。</t>
+          <t>BAT-003 の dump に含まれる。</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -767,15 +767,15 @@
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="63" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>年休の自動付与</t>
+          <t>将来のパーティション/アーカイブ</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>BAT-001（毎日 02:00）。再実行しても二重付与しない設計で、uq_leave_balances_1 が DB 側の最終保証（手動付与と同時に走っても重複行は入らない）。</t>
+          <t>当面不要（年 1,000 件）。5 年を超えた失効済み行は別表へ退避（管理簿の保存期間を満たす範囲で）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -783,15 +783,15 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="10" t="n"/>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>棚卸</t>
+          <t>年休の自動付与</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>年度末に 10章の「消化超過」「失効間近」SQL で確認。</t>
+          <t>BAT-001（毎日 02:00）。再実行しても二重付与しない設計で、uq_leave_balances_1 が DB 側の最終保証（手動付与と同時に走っても重複行は入らない）。</t>
         </is>
       </c>
       <c r="C6" s="9" t="n"/>
@@ -799,15 +799,15 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="48.5" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>バックアップ（BAT-003）</t>
+          <t>棚卸</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>年度末に 10章の「消化超過」「失効間近」SQL で確認。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -815,15 +815,15 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48.5" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>マイグレーション</t>
+          <t>バックアップ（BAT-003）</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -831,79 +831,63 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>マイグレーション</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1・V2（祝日の初期データ）は適用後に編集せず、列追加・索引追加は次の版 V3__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>9.2 既知課題・未決事項（未解決のもの。解消済みは 9.2b）</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>推奨対応</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="77.5" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>C-3</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
     </row>
@@ -971,7 +955,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -984,7 +968,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1003,420 +987,456 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="63" customHeight="1">
+    <row r="16" ht="106.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>C-7</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>保存期間 5 年を超えたデータの自動削除・アーカイブが未実装</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §9（決定 6）は勤怠・申請・監査ログの保存期間を 5 年（設定値）とし、BAT-005『監査ログ／履歴の保存期間管理（アーカイブ）』を計画している。現行の backend には削除・アーカイブ処理も保存期間の設定値も無く、業務データは物理削除しない（例外は通知・祝日・再提出時の承認ステップ）。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始から 5 年間は影響しない。5 年を超えた後の扱い（残す／消す・退避）の手順が無く、運用者の判断になる。件数は 5 年で 4 表合計約 45 万行規模で、容量・性能上の問題にはなりにくい。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始（2026 年）の 5 年後（2031 年）までに、BAT-005 の設計・実装、または手動の退避 SQL の手順を決める。それまでは『消さずに保持する』方針で運用する（5 年はこの方針の目安）。</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="135.5" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>U-5</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>開発用シードの実行条件がプロパティの有無だけで、Spring プロファイルで制限していない</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>DevDataInitializer・DevLeaveBalanceInitializer は @Profile を持たず、kintaiflow.dev.seed-password が空でないことだけで動く。この値は application-local.properties（Git 管理外。application.properties が optional で読み込む）または環境変数 KINTAIFLOW_DEV_SEED_PASSWORD（Docker Compose の .env の DEV_SEED_PASSWORD）で設定できる。作成は users が 0 件のとき（年休付与は leave_balances が 0 件のとき）に限る。</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>本番で users が空のまま seed-password を設定して初回起動すると、全員が同じパスワードの架空ユーザー 100 名（admin@example.com は ADMIN）が作られる。</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>本番では DEV_SEED_PASSWORD を空にして初回起動する（運用。.env.example も空欄）。コード側で @Profile の付与や本番での起動拒否を検討する（コード変更のため本書の範囲外）。確認 SQL：users の @example.com が 0 件であること。</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>LT-3</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48.5" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="19" ht="48.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>LB-2</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>残日数の整合 CHECK が無い</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>granted_days &gt; 0、used_days &gt;= 0、used_days &lt;= granted_days、expires_on &gt; granted_on を DB が保証しない。</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>consume/restore のバグや手動更新で used_days が付与を超える・負になる。</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>CHECK 4 本を追加（ck_lb_days, ck_lb_period）。</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20" ht="48.5" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>LB-4</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>消化の内訳が残らない</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>consume は FIFO で複数の付与行から引くが、どの行から何日引いたかを記録しない（ONL-013 既知の制約）。</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>取消（restore）時に元の行へ正確に戻せない。監査証跡が無い。</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>leave_balance_usages（request_id, leave_balance_id, days）の追加を検討。</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>LB-5</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>付与・調整の理由を保存する列が無い</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>ONL-017 D-2：note は通知本文に使うだけで DB に保存しない。</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>調整履歴で理由を追えない。</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>note VARCHAR(200) 列の追加（ONL-017 将来課題）。</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="22" ht="63" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>LB-6</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>idx_lb_user が uq_leave_balances_1 に包含されて冗長</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>uq_leave_balances_1 (user_id, leave_type_id, granted_on) の先頭 2 列が idx_lb_user (user_id, leave_type_id) と同一で、残日数合計・FIFO 消化・付与履歴の検索はどちらでも賄える。</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>書込み時の索引更新とストレージが無駄（影響は小さい）。</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>DROP INDEX idx_lb_user;</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="106.5" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26" ht="106.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>updated_at が更新時に自動更新されない</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="92" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="27" ht="135.5" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="48.5" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="28" ht="135.5" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48.5" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>LB-1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>(user_id, leave_type_id, granted_on) の UNIQUE が無い</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>uq_leave_balances_1 を追加。ONL-017 は UNIQUE 違反を E-013 に変換、BAT-001 の冪等チェックと合わせて二重付与を DB が保証する。</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>UNIQUE が先頭 2 列を包含するため idx_lb_user が冗長に（課題 LB-6）。</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>leave_balances</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="63" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>LB-3</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>失効日 expires_on の境界判定が処理間で不一致</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>全処理を expires_on &gt;= 基準日（失効日当日までは有効）に統一。ONL-005/007/010/013/017/022 と BAT の判定が一致し、申請時と承認時で残日数がずれない。</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>leave_balances</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>9.3 ONL 規格が挙げた既知の制約・未対応（この表を使う処理の security 欄から抜粋）</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>内容（原文抜粋）</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>ONL-007</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
-        </is>
-      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約（今後）</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>内容（原文抜粋）</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -1426,7 +1446,7 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -1436,17 +1456,17 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>承認待ち申請が確保する日数は差し引かない（承認時に E-004 となる）。consume の内訳（どの行から何日引いたか）は記録しない。年5日は申請の start_date で期間判定する簡略化。used_days の更新時も updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で自動更新される。</t>
+          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="10" t="n"/>
     </row>
-    <row r="35" ht="48.5" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -1456,31 +1476,92 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="10" t="n"/>
     </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（今後）</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>ONL-013</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>承認待ち申請が確保する日数は差し引かない（承認時に E-004 となる）。consume の内訳（どの行から何日引いたか）は記録しない。年5日は申請の start_date で期間判定する簡略化。used_days の更新時も updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で自動更新される。</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="48.5" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C38:F38"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1757,10 +1838,10 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ V2__seed_holidays.sql ＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -1796,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1855,6 +1936,29 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="48.5" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>運用に開発用の初期付与（DevLeaveBalanceInitializer：年次有給休暇 20 日・当年度 4/1 付与・失効は付与の 2 年後）を追記。V2 追加に伴いデータ例の前提を更新。課題 U-5 を対象に追加。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1869,7 +1973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F36"/>
+  <dimension ref="A2:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1932,7 +2036,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway の V1__init_schema.sql（backend/src/main/resources/db/migration）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -2052,15 +2156,15 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Entity クラス</t>
+          <t>初期データ</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>com.example.kintaiflow.entity.LeaveBalance</t>
+          <t>V1・V2 の SQL では作らない。開発環境のみ DevLeaveBalanceInitializer が、seed-password 設定済み・leave_balances が 0 件のとき、ACTIVE の全ユーザーへ年次有給休暇 20 日（当年度 4/1 付与）を作る（9.1 運用）。</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -2068,15 +2172,15 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
-    <row r="14" ht="34" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Entity クラス</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>repository.LeaveBalanceRepository（sumRemainingDays / findValidBalances / 行ロック付き検索 / findGrantRows / existsByUserIdAndLeaveTypeIdAndGrantedOn / findByIdForUpdate）</t>
+          <t>com.example.kintaiflow.entity.LeaveBalance</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -2084,84 +2188,76 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>repository.LeaveBalanceRepository（sumRemainingDays / findValidBalances / findConsumableForUpdate / findRestorableForUpdate / findGrantRowsAll / findGrantRowsByType / findAlertBaseRows / existsByUserIdAndLeaveTypeIdAndGrantedOn / findByIdForUpdate）</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>1.2 主な利用処理（オンライン処理・バッチ）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>API / 種別</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>備考（規格 tables の注記ほか）</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ONL-005</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>申請作成</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>API-005 POST /api/requests</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>ONL-007</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>申請詳細取得</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>API-007 GET /api/requests/{id}</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2175,45 +2271,41 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>申請詳細取得</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>API-010 POST /api/approvals/{id}/approve</t>
+          <t>API-007 GET /api/requests/{id}</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>R/U</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>（LeaveBalanceService 経由）</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>休暇残日数取得</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>API-013 GET /api/leave-balances</t>
+          <t>API-010 POST /api/approvals/{id}/approve</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2221,28 +2313,32 @@
           <t>R/U</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>（LeaveBalanceService 経由）</t>
+        </is>
+      </c>
       <c r="F21" s="10" t="n"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-013</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>休暇付与</t>
+          <t>休暇残日数取得</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>API-017 GET/POST/PUT /api/admin/leave-grants[/{id}]</t>
+          <t>API-013 GET /api/leave-balances</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C/R/U</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr"/>
@@ -2251,46 +2347,46 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>申請提出</t>
+          <t>休暇付与</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>API-022 POST /api/requests/{id}/submit</t>
+          <t>API-017 GET/POST/PUT /api/admin/leave-grants[/{id}]</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C/R/U</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="24" ht="19.5" customHeight="1">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>申請提出</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>バッチ</t>
+          <t>API-022 POST /api/requests/{id}/submit</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>C/R</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr"/>
@@ -2299,12 +2395,12 @@
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>年次有給休暇 自動付与</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -2314,86 +2410,90 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C/R</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="34" customHeight="1">
+    <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>バッチ</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2403,17 +2503,17 @@
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-003</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>テーブル定義書（基本）</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>論理名・基本項目</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -2423,17 +2523,17 @@
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>コード定義書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>コード値と状態遷移の基本設計</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2443,17 +2543,17 @@
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-001</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>オンライン設計書</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -2463,17 +2563,17 @@
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-001</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>オンライン設計書</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ONL-001〜022 の概要</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
@@ -2483,17 +2583,17 @@
     <row r="35" ht="19.5" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-DD-ONL-xxx</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>オンライン詳細設計書</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
@@ -2503,33 +2603,52 @@
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>KF-DD-004 / BAT</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>バッチ設計書</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>BAT-001〜003 の使用</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
     </row>
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C37:F37"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="E20:F20"/>
@@ -2537,18 +2656,20 @@
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="E22:F22"/>
@@ -2589,7 +2710,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（V1__init_schema.sql から自動生成）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3213,7 +3334,7 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は V1__init_schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -3260,7 +3381,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（V1__init_schema.sql の定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3630,7 +3751,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>CREATE INDEX（schema.sql）</t>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3747,7 +3868,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1・V2＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B25" s="9" t="n"/>
@@ -5741,7 +5862,7 @@
       <c r="B3" s="7" t="inlineStr">
         <is>
           <t>山田 太郎（taro@example.com、入社 2024-04-01）の年次有給休暇：6か月後の 2024-10-01 に 10 日、1 年 6 か月後の 2025-10-01 に 11 日（付与日数表）。失効は付与から 2 年。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+例の INSERT は V1・V2 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
